--- a/confluent-cloud-clusterlink/calculadora-privatelink.xlsx
+++ b/confluent-cloud-clusterlink/calculadora-privatelink.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Calculadora" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Tarifas" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Regiones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Listas" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Listas" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Consideraciones" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="AWS">Regiones!$B$2:$B$28</definedName>
-    <definedName name="Azure">Regiones!$B$29:$B$60</definedName>
-    <definedName name="GCP">Regiones!$B$61:$B$90</definedName>
+    <definedName name="Cloud_AWS">Regiones!$B$2:$B$28</definedName>
+    <definedName name="Cloud_Azure">Regiones!$B$29:$B$60</definedName>
+    <definedName name="Cloud_GCP">Regiones!$B$61:$B$90</definedName>
     <definedName name="AllClaves">Regiones!$G$2:$G$90</definedName>
     <definedName name="AllClouds">Listas!$A$2:$A$4</definedName>
     <definedName name="CL_PUBLIC_HOUR">Tarifas!$B$6</definedName>
@@ -285,7 +285,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -298,6 +297,7 @@
     <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -459,11 +459,6 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Calculadora'!J32</f>
-            </strRef>
-          </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="00C4CC"/>
@@ -898,7 +893,6 @@
           <t>Azure</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n"/>
       <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Cloud</t>
@@ -909,23 +903,22 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="G5" s="8" t="n"/>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>USD / mes</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>Cómo se calcula</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>Bloque</t>
         </is>
@@ -942,7 +935,6 @@
           <t>eastus2</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n"/>
       <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Region</t>
@@ -953,21 +945,20 @@
           <t>us-east-1</t>
         </is>
       </c>
-      <c r="G6" s="8" t="n"/>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>CKU cluster A</t>
         </is>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="10">
         <f>$B$8*CKU_HOUR*$F$17*HOURS_MONTH</f>
         <v/>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="11">
         <f>$B$8&amp;" CKU × "&amp;TEXT(CKU_HOUR*$F$17,"$0.00")&amp;"/h × "&amp;HOURS_MONTH&amp;"h"</f>
         <v/>
       </c>
-      <c r="L6" s="13" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>Confluent</t>
         </is>
@@ -984,7 +975,6 @@
           <t>Multi-zone</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n"/>
       <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Availability</t>
@@ -995,21 +985,20 @@
           <t>Multi-zone</t>
         </is>
       </c>
-      <c r="G7" s="8" t="n"/>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>CKU cluster B</t>
         </is>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="10">
         <f>$F$8*CKU_HOUR*$F$20*HOURS_MONTH</f>
         <v/>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="11">
         <f>$F$8&amp;" CKU × "&amp;TEXT(CKU_HOUR*$F$20,"$0.00")&amp;"/h × "&amp;HOURS_MONTH&amp;"h"</f>
         <v/>
       </c>
-      <c r="L7" s="13" t="inlineStr">
+      <c r="L7" s="12" t="inlineStr">
         <is>
           <t>Confluent</t>
         </is>
@@ -1021,33 +1010,31 @@
           <t>CKU</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="8" t="n"/>
       <c r="E8" s="6" t="inlineStr">
         <is>
           <t>CKU</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="8" t="n"/>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Kafka ingress clientes A</t>
         </is>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="10">
         <f>$B$10*KAFKA_IN_GB*$F$17</f>
         <v/>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="11">
         <f>$B$10&amp;" GB × "&amp;TEXT(KAFKA_IN_GB*$F$17,"$0.00")</f>
         <v/>
       </c>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="L8" s="12" t="inlineStr">
         <is>
           <t>Confluent</t>
         </is>
@@ -1059,33 +1046,31 @@
           <t>VNets / VPCs cliente</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="8" t="n"/>
       <c r="E9" s="6" t="inlineStr">
         <is>
           <t>VNets / VPCs cliente</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="8" t="n"/>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Kafka ingress clientes B</t>
         </is>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="10">
         <f>$F$10*KAFKA_IN_GB*$F$20</f>
         <v/>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="11">
         <f>$F$10&amp;" GB × "&amp;TEXT(KAFKA_IN_GB*$F$20,"$0.00")</f>
         <v/>
       </c>
-      <c r="L9" s="13" t="inlineStr">
+      <c r="L9" s="12" t="inlineStr">
         <is>
           <t>Confluent</t>
         </is>
@@ -1097,33 +1082,31 @@
           <t>Produce cliente (GB/mes)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="13" t="n">
         <v>400</v>
       </c>
-      <c r="C10" s="8" t="n"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Produce cliente (GB/mes)</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="8" t="n"/>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>Kafka egress clientes A</t>
         </is>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="10">
         <f>$B$11*KAFKA_OUT_GB*$F$17</f>
         <v/>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="11">
         <f>$B$11&amp;" GB × "&amp;TEXT(KAFKA_OUT_GB*$F$17,"$0.00")</f>
         <v/>
       </c>
-      <c r="L10" s="13" t="inlineStr">
+      <c r="L10" s="12" t="inlineStr">
         <is>
           <t>Confluent</t>
         </is>
@@ -1135,33 +1118,31 @@
           <t>Consume cliente (GB/mes)</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="13" t="n">
         <v>800</v>
       </c>
-      <c r="C11" s="8" t="n"/>
       <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Consume cliente (GB/mes)</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="13" t="n">
         <v>400</v>
       </c>
-      <c r="G11" s="8" t="n"/>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>Kafka egress clientes B</t>
         </is>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="10">
         <f>$F$11*KAFKA_OUT_GB*$F$20</f>
         <v/>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="11">
         <f>$F$11&amp;" GB × "&amp;TEXT(KAFKA_OUT_GB*$F$20,"$0.00")</f>
         <v/>
       </c>
-      <c r="L11" s="13" t="inlineStr">
+      <c r="L11" s="12" t="inlineStr">
         <is>
           <t>Confluent</t>
         </is>
@@ -1173,53 +1154,51 @@
           <t>Storage pre-RF (GB)</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B12" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="C12" s="8" t="n"/>
       <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Storage pre-RF (GB)</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="G12" s="8" t="n"/>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>Storage A (× RF)</t>
         </is>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="10">
         <f>$B$12*RF*STORAGE_GB_MONTH</f>
         <v/>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="11">
         <f>$B$12&amp;" GB pre × "&amp;RF&amp;" × "&amp;TEXT(STORAGE_GB_MONTH,"$0.00")</f>
         <v/>
       </c>
-      <c r="L12" s="13" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
         <is>
           <t>Confluent</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>Storage B (× RF)</t>
         </is>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="10">
         <f>$F$12*RF*STORAGE_GB_MONTH</f>
         <v/>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="11">
         <f>$F$12&amp;" GB pre × "&amp;RF&amp;" × "&amp;TEXT(STORAGE_GB_MONTH,"$0.00")</f>
         <v/>
       </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t>Confluent</t>
         </is>
@@ -1233,27 +1212,27 @@
       </c>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Diagnóstico (fórmulas)</t>
         </is>
       </c>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>Cluster link hourly A</t>
         </is>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="10">
         <f>$F$25*$F$22*HOURS_MONTH</f>
         <v/>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="11">
         <f>TEXT($F$25,"$0.00")&amp;"/h × "&amp;$F$22&amp;" link(s) × "&amp;HOURS_MONTH&amp;"h"</f>
         <v/>
       </c>
-      <c r="L14" s="13" t="inlineStr">
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t>Confluent</t>
         </is>
@@ -1267,35 +1246,33 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Unidirectional A → B</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n"/>
+          <t>Unidirectional</t>
+        </is>
+      </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Premium A</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>IFERROR(INDEX(Regiones!$D$2:$D$90,MATCH($B$5&amp;"|"&amp;$B$6,Regiones!$G$2:$G$90,0)),"NO")</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="n"/>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="F15" s="11">
+        <f>IFERROR(INDEX(Regiones!$D$2:$D$90,MATCH($B$5&amp;"|"&amp;$B$6,Regiones!$G$2:$G$90,0)),"NO")</f>
+        <v/>
+      </c>
+      <c r="G15" s="14" t="n"/>
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>Cluster link hourly B</t>
         </is>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="10">
         <f>$F$26*$F$22*HOURS_MONTH</f>
         <v/>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="11">
         <f>TEXT($F$26,"$0.00")&amp;"/h × "&amp;$F$22&amp;" link(s) × "&amp;HOURS_MONTH&amp;"h"</f>
         <v/>
       </c>
-      <c r="L15" s="13" t="inlineStr">
+      <c r="L15" s="12" t="inlineStr">
         <is>
           <t>Confluent</t>
         </is>
@@ -1307,35 +1284,33 @@
           <t>Mirror A → B (GB/mes)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B16" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="C16" s="8" t="n"/>
       <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Jio A (sin PL)</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>IFERROR(INDEX(Regiones!$E$2:$E$90,MATCH($B$5&amp;"|"&amp;$B$6,Regiones!$G$2:$G$90,0)),"NO")</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="n"/>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="F16" s="11">
+        <f>IFERROR(INDEX(Regiones!$E$2:$E$90,MATCH($B$5&amp;"|"&amp;$B$6,Regiones!$G$2:$G$90,0)),"NO")</f>
+        <v/>
+      </c>
+      <c r="G16" s="14" t="n"/>
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>ClusterLinkingRead A→B</t>
         </is>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="10">
         <f>$F$23*CL_READ_GB*$F$17</f>
         <v/>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="11">
         <f>$F$23&amp;" GB × "&amp;TEXT(CL_READ_GB,"$0.00")&amp;" × "&amp;$F$17</f>
         <v/>
       </c>
-      <c r="L16" s="13" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
         <is>
           <t>Confluent</t>
         </is>
@@ -1347,35 +1322,33 @@
           <t>Mirror B → A (GB/mes)</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B17" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="8" t="n"/>
       <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Multiplier A</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>IFERROR(INDEX(Regiones!$F$2:$F$90,MATCH($B$5&amp;"|"&amp;$B$6,Regiones!$G$2:$G$90,0)),1)</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="n"/>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="F17" s="15">
+        <f>IFERROR(INDEX(Regiones!$F$2:$F$90,MATCH($B$5&amp;"|"&amp;$B$6,Regiones!$G$2:$G$90,0)),1)</f>
+        <v/>
+      </c>
+      <c r="G17" s="14" t="n"/>
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>ClusterLinkingWrite A→B</t>
         </is>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="10">
         <f>$F$23*KAFKA_IN_GB*$F$20</f>
         <v/>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="11">
         <f>$F$23&amp;" GB × dest KafkaNetworkWrite"</f>
         <v/>
       </c>
-      <c r="L17" s="13" t="inlineStr">
+      <c r="L17" s="12" t="inlineStr">
         <is>
           <t>Confluent</t>
         </is>
@@ -1387,64 +1360,62 @@
           <t>Premium B</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>IFERROR(INDEX(Regiones!$D$2:$D$90,MATCH($F$5&amp;"|"&amp;$F$6,Regiones!$G$2:$G$90,0)),"NO")</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="n"/>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="F18" s="11">
+        <f>IFERROR(INDEX(Regiones!$D$2:$D$90,MATCH($F$5&amp;"|"&amp;$F$6,Regiones!$G$2:$G$90,0)),"NO")</f>
+        <v/>
+      </c>
+      <c r="G18" s="14" t="n"/>
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>ClusterLinkingRead B→A</t>
         </is>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="10">
         <f>$F$24*CL_READ_GB*$F$20</f>
         <v/>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="11">
         <f>$F$24&amp;" GB × "&amp;TEXT(CL_READ_GB,"$0.00")&amp;" × "&amp;$F$20</f>
         <v/>
       </c>
-      <c r="L18" s="13" t="inlineStr">
+      <c r="L18" s="12" t="inlineStr">
         <is>
           <t>Confluent</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Cómo usar</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
       <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Jio B (sin PL)</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>IFERROR(INDEX(Regiones!$E$2:$E$90,MATCH($F$5&amp;"|"&amp;$F$6,Regiones!$G$2:$G$90,0)),"NO")</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="n"/>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="F19" s="11">
+        <f>IFERROR(INDEX(Regiones!$E$2:$E$90,MATCH($F$5&amp;"|"&amp;$F$6,Regiones!$G$2:$G$90,0)),"NO")</f>
+        <v/>
+      </c>
+      <c r="G19" s="14" t="n"/>
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>ClusterLinkingWrite B→A</t>
         </is>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="10">
         <f>$F$24*KAFKA_IN_GB*$F$17</f>
         <v/>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="11">
         <f>$F$24&amp;" GB × dest KafkaNetworkWrite"</f>
         <v/>
       </c>
-      <c r="L19" s="13" t="inlineStr">
+      <c r="L19" s="12" t="inlineStr">
         <is>
           <t>Confluent</t>
         </is>
@@ -1455,7 +1426,7 @@
         <is>
           <t>1. Elige Cloud y Region de A y B (el dropdown de Region depende del Cloud).
 2. Multi-zone Dedicated exige mínimo 2 CKU y 3 endpoints (Azure/GCP) o 1 VPCE en 3 AZ (AWS).
-3. Dirección: Unidirectional cobra 1 link; Bidirectional cobra 2. El objeto se cobra aunque GB = 0.
+3. Dirección: Unidirectional = 1 link; Bidirectional = 2; None = 0. El objeto se cobra aunque GB = 0.
 4. Cross-cloud + ambos private: hourly $2.50, o $5.00 si Premium (hoja Regiones).
 5. Intra-cloud private: $0.50/h × multiplier de esa región.
 6. ClusterLinkingWrite = Kafka ingress del destination. No se cobra Kafka ingress extra.
@@ -1472,22 +1443,21 @@
           <t>Multiplier B</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>IFERROR(INDEX(Regiones!$F$2:$F$90,MATCH($F$5&amp;"|"&amp;$F$6,Regiones!$G$2:$G$90,0)),1)</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="n"/>
+      <c r="F20" s="15">
+        <f>IFERROR(INDEX(Regiones!$F$2:$F$90,MATCH($F$5&amp;"|"&amp;$F$6,Regiones!$G$2:$G$90,0)),1)</f>
+        <v/>
+      </c>
+      <c r="G20" s="14" t="n"/>
       <c r="I20" s="17" t="inlineStr">
         <is>
           <t>CSP endpoints A</t>
         </is>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="10">
         <f>$F$29*CSP_PE_HOUR*HOURS_MONTH+($B$10+$B$11)*CSP_PE_GB</f>
         <v/>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="11">
         <f>$F$29&amp;" unidades + "&amp;($B$10+$B$11)&amp;" GB cliente"</f>
         <v/>
       </c>
@@ -1503,21 +1473,21 @@
           <t>Cross-cloud</t>
         </is>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="11">
         <f>$B$5&lt;&gt;$F$5</f>
         <v/>
       </c>
-      <c r="G21" s="8" t="n"/>
+      <c r="G21" s="14" t="n"/>
       <c r="I21" s="17" t="inlineStr">
         <is>
           <t>CSP endpoints B</t>
         </is>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="10">
         <f>$F$30*CSP_PE_HOUR*HOURS_MONTH+($F$10+$F$11)*CSP_PE_GB</f>
         <v/>
       </c>
-      <c r="K21" s="12">
+      <c r="K21" s="11">
         <f>$F$30&amp;" unidades + "&amp;($F$10+$F$11)&amp;" GB cliente"</f>
         <v/>
       </c>
@@ -1534,10 +1504,10 @@
         </is>
       </c>
       <c r="F22" s="19">
-        <f>IF($B$15="Sin Cluster Linking",0,IF($B$15="Bidirectional",2,1))</f>
-        <v/>
-      </c>
-      <c r="G22" s="8" t="n"/>
+        <f>IF(OR($B$15="None",$B$15="Sin Cluster Linking"),0,IF($B$15="Bidirectional",2,1))</f>
+        <v/>
+      </c>
+      <c r="G22" s="14" t="n"/>
       <c r="I22" s="20" t="inlineStr">
         <is>
           <t>Subtotal Confluent</t>
@@ -1555,16 +1525,16 @@
         </is>
       </c>
       <c r="F23" s="19">
-        <f>IF($B$15="Sin Cluster Linking",0,$B$16)</f>
-        <v/>
-      </c>
-      <c r="G23" s="8" t="n"/>
+        <f>IF(OR($B$15="None",$B$15="Sin Cluster Linking"),0,$B$16)</f>
+        <v/>
+      </c>
+      <c r="G23" s="14" t="n"/>
       <c r="I23" s="20" t="inlineStr">
         <is>
           <t>Subtotal CSP</t>
         </is>
       </c>
-      <c r="J23" s="11">
+      <c r="J23" s="10">
         <f>SUMIF($L$6:$L$21,"CSP",$J$6:$J$21)</f>
         <v/>
       </c>
@@ -1579,7 +1549,7 @@
         <f>IF($B$15="Bidirectional",$B$17,0)</f>
         <v/>
       </c>
-      <c r="G24" s="8" t="n"/>
+      <c r="G24" s="14" t="n"/>
       <c r="I24" s="22" t="inlineStr">
         <is>
           <t>TOTAL USD / mes</t>
@@ -1605,7 +1575,7 @@
         <f>IF($F$22=0,0,IF($F$21,IF($F$15="SI",CL_XCLOUD_PREMIUM_HOUR,CL_XCLOUD_HOUR),CL_PRIVATE_HOUR*$F$17))</f>
         <v/>
       </c>
-      <c r="G25" s="8" t="n"/>
+      <c r="G25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="E26" s="6" t="inlineStr">
@@ -1617,8 +1587,8 @@
         <f>IF($F$22=0,0,IF($F$21,IF($F$18="SI",CL_XCLOUD_PREMIUM_HOUR,CL_XCLOUD_HOUR),CL_PRIVATE_HOUR*$F$20))</f>
         <v/>
       </c>
-      <c r="G26" s="8" t="n"/>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="G26" s="14" t="n"/>
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Private Link a provisionar</t>
         </is>
@@ -1634,18 +1604,18 @@
         <f>IF($B$7="Single-zone",1,3)</f>
         <v/>
       </c>
-      <c r="G27" s="8" t="n"/>
+      <c r="G27" s="14" t="n"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J27" s="12">
+      <c r="J27" s="11">
         <f>$F$31&amp;" × "&amp;$F$33</f>
         <v/>
       </c>
       <c r="K27" s="26" t="n"/>
-      <c r="L27" s="8" t="n"/>
+      <c r="L27" s="14" t="n"/>
     </row>
     <row r="28">
       <c r="E28" s="6" t="inlineStr">
@@ -1657,18 +1627,18 @@
         <f>IF($F$7="Single-zone",1,3)</f>
         <v/>
       </c>
-      <c r="G28" s="8" t="n"/>
+      <c r="G28" s="14" t="n"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J28" s="12">
+      <c r="J28" s="11">
         <f>$F$32&amp;" × "&amp;$F$34</f>
         <v/>
       </c>
       <c r="K28" s="26" t="n"/>
-      <c r="L28" s="8" t="n"/>
+      <c r="L28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="E29" s="6" t="inlineStr">
@@ -1677,21 +1647,21 @@
         </is>
       </c>
       <c r="F29" s="19">
-        <f>IF($B$5="AWS",$B$9*$F$27,$B$9*$F$27)</f>
-        <v/>
-      </c>
-      <c r="G29" s="8" t="n"/>
+        <f>$B$9*$F$27</f>
+        <v/>
+      </c>
+      <c r="G29" s="14" t="n"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>DNS por cluster</t>
         </is>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="11">
         <f>IF($B$7="Single-zone","* + 1 zonal (A records)","* + 3 zonales (A/CNAME). No hardcodear brokers.")</f>
         <v/>
       </c>
       <c r="K29" s="26" t="n"/>
-      <c r="L29" s="8" t="n"/>
+      <c r="L29" s="14" t="n"/>
     </row>
     <row r="30">
       <c r="E30" s="6" t="inlineStr">
@@ -1703,18 +1673,18 @@
         <f>$F$9*$F$28</f>
         <v/>
       </c>
-      <c r="G30" s="8" t="n"/>
+      <c r="G30" s="14" t="n"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>CKU A / B vs guía</t>
         </is>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="11">
         <f>$B$8&amp;" / "&amp;$F$8&amp;"  (sugerido "&amp;$F$38&amp;" / "&amp;$F$39&amp;")")</f>
         <v/>
       </c>
       <c r="K30" s="26" t="n"/>
-      <c r="L30" s="8" t="n"/>
+      <c r="L30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="E31" s="6" t="inlineStr">
@@ -1726,7 +1696,7 @@
         <f>IF($B$5="AWS",$B$9,$B$9*$F$27)</f>
         <v/>
       </c>
-      <c r="G31" s="8" t="n"/>
+      <c r="G31" s="14" t="n"/>
     </row>
     <row r="32">
       <c r="E32" s="6" t="inlineStr">
@@ -1738,13 +1708,13 @@
         <f>IF($F$5="AWS",$F$9,$F$9*$F$28)</f>
         <v/>
       </c>
-      <c r="G32" s="8" t="n"/>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="G32" s="14" t="n"/>
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Gráfico</t>
         </is>
       </c>
-      <c r="J32" s="9" t="n"/>
+      <c r="J32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="E33" s="6" t="inlineStr">
@@ -1752,11 +1722,11 @@
           <t>Tipo endpoint A</t>
         </is>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="11">
         <f>IF($B$5="AWS","VPC endpoint (1 × N AZ)",IF($B$5="Azure","Private Endpoints","PSC endpoints"))</f>
         <v/>
       </c>
-      <c r="G33" s="8" t="n"/>
+      <c r="G33" s="14" t="n"/>
       <c r="I33" s="27" t="inlineStr">
         <is>
           <t>CKU</t>
@@ -1773,11 +1743,11 @@
           <t>Tipo endpoint B</t>
         </is>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="11">
         <f>IF($F$5="AWS","VPC endpoint (1 × N AZ)",IF($F$5="Azure","Private Endpoints","PSC endpoints"))</f>
         <v/>
       </c>
-      <c r="G34" s="8" t="n"/>
+      <c r="G34" s="14" t="n"/>
       <c r="I34" s="27" t="inlineStr">
         <is>
           <t>Kafka in/out + storage</t>
@@ -1794,11 +1764,11 @@
           <t>Región válida A</t>
         </is>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="11">
         <f>IF(COUNTIFS(Regiones!$A$2:$A$90,$B$5,Regiones!$B$2:$B$90,$B$6)=1,"OK","Region no coincide con cloud")</f>
         <v/>
       </c>
-      <c r="G35" s="8" t="n"/>
+      <c r="G35" s="14" t="n"/>
       <c r="I35" s="27" t="inlineStr">
         <is>
           <t>Cluster Linking</t>
@@ -1815,11 +1785,11 @@
           <t>Región válida B</t>
         </is>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="11">
         <f>IF(COUNTIFS(Regiones!$A$2:$A$90,$F$5,Regiones!$B$2:$B$90,$F$6)=1,"OK","Region no coincide con cloud")</f>
         <v/>
       </c>
-      <c r="G36" s="8" t="n"/>
+      <c r="G36" s="14" t="n"/>
       <c r="I36" s="27" t="inlineStr">
         <is>
           <t>CSP Private Link</t>
@@ -1836,12 +1806,11 @@
           <t>Mismo Organization</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>OBLIGATORIO si ambos son private Dedicated</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="n"/>
+      <c r="F37" s="11">
+        <f>OBLIGATORIO si ambos son private Dedicated</f>
+        <v/>
+      </c>
+      <c r="G37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="E38" s="29" t="inlineStr">
@@ -1853,7 +1822,7 @@
         <f>MAX(IF($B$7="Multi-zone",2,1),ROUNDUP(MAX((($B$10+$F$24)*1024)/(HOURS_MONTH*3600)/CKU_IN_MBPS,(($B$11+$F$23)*1024)/(HOURS_MONTH*3600)/CKU_OUT_MBPS),0))</f>
         <v/>
       </c>
-      <c r="G38" s="8" t="n"/>
+      <c r="G38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="E39" s="29" t="inlineStr">
@@ -1865,7 +1834,7 @@
         <f>MAX(IF($F$7="Multi-zone",2,1),ROUNDUP(MAX((($F$10+$F$23)*1024)/(HOURS_MONTH*3600)/CKU_IN_MBPS,(($F$11+$F$24)*1024)/(HOURS_MONTH*3600)/CKU_OUT_MBPS),0))</f>
         <v/>
       </c>
-      <c r="G39" s="8" t="n"/>
+      <c r="G39" s="14" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="E40" s="29" t="inlineStr">
@@ -1874,70 +1843,51 @@
         </is>
       </c>
       <c r="F40" s="30">
-        <f>TEXTJOIN(" · ",TRUE,IF(OR($F$16="SI",$F$19="SI"),"Jio: no Private Link",""),IF(OR($B$8&lt;$F$38,$F$8&lt;$F$39),"CKU por debajo de la guía",""),IF(OR(AND($B$7="Multi-zone",$B$8&lt;2),AND($F$7="Multi-zone",$F$8&lt;2)),"Multi-zone exige 2 CKU",""),IF($F$21,"Cross-cloud private Cluster Linking","Intra-cloud private"),IF(OR($F$15="SI",$F$18="SI"),"Premium region $5.00/h",""),IF($F$22=2,"Bidirectional = 2 links",""))</f>
-        <v/>
-      </c>
-      <c r="G40" s="8" t="n"/>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(IF(OR($F$16="SI",$F$19="SI"),"Jio: no Private Link · ","")&amp;IF(OR($B$8&lt;$F$38,$F$8&lt;$F$39),"CKU por debajo de la guía · ","")&amp;IF(OR(AND($B$7="Multi-zone",$B$8&lt;2),AND($F$7="Multi-zone",$F$8&lt;2)),"Multi-zone exige 2 CKU · ","")&amp;IF($F$21,"Cross-cloud private Cluster Linking · ","Intra-cloud private · ")&amp;IF(OR($F$15="SI",$F$18="SI"),"Premium region $5.00/h · ","")&amp;IF($F$22=2,"Bidirectional = 2 links · ","")&amp;IF(OR($F$35&lt;&gt;"OK",$F$36&lt;&gt;"OK"),"Region no coincide con cloud","")," ·  "," · "), " ·", ""))</f>
+        <v/>
+      </c>
+      <c r="G40" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B7:C7"/>
+  <mergeCells count="41">
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="I4:L4"/>
     <mergeCell ref="J27:L27"/>
-    <mergeCell ref="F6:G6"/>
     <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B12:C12"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="F12:G12"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="F5:G5"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="F32:G32"/>
-    <mergeCell ref="B17:C17"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="B8:C8"/>
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F8:G8"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="I26:L26"/>
     <mergeCell ref="F38:G38"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="F28:G28"/>
-    <mergeCell ref="B9:C9"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F9:G9"/>
     <mergeCell ref="I22"/>
+    <mergeCell ref="A20:C37"/>
     <mergeCell ref="J29:L29"/>
-    <mergeCell ref="A20:C37"/>
-    <mergeCell ref="B6:C6"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="F39:G39"/>
-    <mergeCell ref="B15:C15"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="J28:L28"/>
-    <mergeCell ref="B5:C5"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="E4:G4"/>
     <mergeCell ref="J30:L30"/>
@@ -1978,10 +1928,10 @@
       <formula1>=Listas!$C$2:$C$4</formula1>
     </dataValidation>
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Region A" error="Elige una región del cloud de la celda B5. Cambia Cloud primero." type="list">
-      <formula1>=INDIRECT($B$5)</formula1>
+      <formula1>=INDIRECT("Cloud_"&amp;$B$5)</formula1>
     </dataValidation>
     <dataValidation sqref="F6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Region B" error="Elige una región del cloud de la celda F5. Cambia Cloud primero." type="list">
-      <formula1>=INDIRECT($F$5)</formula1>
+      <formula1>=INDIRECT("Cloud_"&amp;$F$5)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5658,7 +5608,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Unidirectional A → B</t>
+          <t>Unidirectional</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5637,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sin Cluster Linking</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5686,12 @@
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Billing Dimensions</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Hourly público</t>
         </is>
@@ -5753,12 +5703,12 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Billing Dimensions</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Hourly private intra-cloud</t>
         </is>
@@ -5770,12 +5720,12 @@
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Billing Dimensions</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Hourly cross-cloud private</t>
         </is>
@@ -5787,12 +5737,12 @@
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Billing Dimensions</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>ClusterLinkingWrite</t>
         </is>
@@ -5804,12 +5754,12 @@
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Billing Dimensions</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>ClusterLinkingRead</t>
         </is>
@@ -5821,12 +5771,12 @@
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Billing Dimensions</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Se cobra el objeto</t>
         </is>
@@ -5838,12 +5788,12 @@
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Billing Dimensions</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Regional multiplier</t>
         </is>
@@ -5855,12 +5805,12 @@
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Billing Dimensions</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Storage RF=3</t>
         </is>
@@ -5872,12 +5822,12 @@
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Billing Dimensions</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>GiB y UTC</t>
         </is>
@@ -5889,7 +5839,7 @@
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Cluster Linking private</t>
         </is>
@@ -5906,12 +5856,12 @@
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Cluster Linking private</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Dedicated ↔ Dedicated private</t>
         </is>
@@ -5923,12 +5873,12 @@
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Cluster Linking private</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Private → Public</t>
         </is>
@@ -5940,12 +5890,12 @@
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Regions</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Premium region</t>
         </is>
@@ -5957,7 +5907,7 @@
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Regions</t>
         </is>
@@ -5974,12 +5924,12 @@
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Cluster types</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>CKU</t>
         </is>
@@ -5991,12 +5941,12 @@
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Cluster types</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Tope CKU</t>
         </is>
@@ -6008,12 +5958,12 @@
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Azure PL Dedicated</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Endpoints</t>
         </is>
@@ -6025,12 +5975,12 @@
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Azure PL Dedicated</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>DNS</t>
         </is>
@@ -6042,7 +5992,7 @@
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Azure PL Dedicated</t>
         </is>
@@ -6059,12 +6009,12 @@
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>AWS PL Dedicated</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>AZ matching</t>
         </is>
@@ -6076,12 +6026,12 @@
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>AWS PL Dedicated</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Sin PL cross-region</t>
         </is>
@@ -6093,12 +6043,12 @@
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>GCP PSC Dedicated</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Endpoints</t>
         </is>
@@ -6110,12 +6060,12 @@
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>GCP PSC Dedicated</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Attach same-region</t>
         </is>
@@ -6127,12 +6077,12 @@
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>PL Dedicated (los 3)</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Internet residual</t>
         </is>
@@ -6144,12 +6094,12 @@
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>PL Dedicated (los 3)</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Connectors</t>
         </is>
@@ -6161,12 +6111,12 @@
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>PL Dedicated (los 3)</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Flink / SR</t>
         </is>

--- a/confluent-cloud-clusterlink/calculadora-privatelink.xlsx
+++ b/confluent-cloud-clusterlink/calculadora-privatelink.xlsx
@@ -31,7 +31,7 @@
     <definedName name="CSP_PE_HOUR">Tarifas!$B$18</definedName>
     <definedName name="CSP_PE_GB">Tarifas!$B$19</definedName>
     <definedName name="HOURS_MONTH">Tarifas!$B$20</definedName>
-    <definedName name="RF">Tarifas!$B$21</definedName>
+    <definedName name="REPL_FACTOR">Tarifas!$B$21</definedName>
     <definedName name="CKU_IN_MBPS">Tarifas!$B$22</definedName>
     <definedName name="CKU_OUT_MBPS">Tarifas!$B$23</definedName>
     <definedName name="CKU_PARTITIONS">Tarifas!$B$24</definedName>
@@ -1171,11 +1171,11 @@
         </is>
       </c>
       <c r="J12" s="10">
-        <f>$B$12*RF*STORAGE_GB_MONTH</f>
+        <f>$B$12*REPL_FACTOR*STORAGE_GB_MONTH</f>
         <v/>
       </c>
       <c r="K12" s="11">
-        <f>$B$12&amp;" GB pre × "&amp;RF&amp;" × "&amp;TEXT(STORAGE_GB_MONTH,"$0.00")</f>
+        <f>$B$12&amp;" GB pre x "&amp;REPL_FACTOR&amp;" x "&amp;TEXT(STORAGE_GB_MONTH,"$0.00")</f>
         <v/>
       </c>
       <c r="L12" s="12" t="inlineStr">
@@ -1191,11 +1191,11 @@
         </is>
       </c>
       <c r="J13" s="10">
-        <f>$F$12*RF*STORAGE_GB_MONTH</f>
+        <f>$F$12*REPL_FACTOR*STORAGE_GB_MONTH</f>
         <v/>
       </c>
       <c r="K13" s="11">
-        <f>$F$12&amp;" GB pre × "&amp;RF&amp;" × "&amp;TEXT(STORAGE_GB_MONTH,"$0.00")</f>
+        <f>$F$12&amp;" GB pre x "&amp;REPL_FACTOR&amp;" x "&amp;TEXT(STORAGE_GB_MONTH,"$0.00")</f>
         <v/>
       </c>
       <c r="L13" s="12" t="inlineStr">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="J27" s="11">
-        <f>$F$31&amp;" × "&amp;$F$33</f>
+        <f>$F$31&amp;" x "&amp;$F$33</f>
         <v/>
       </c>
       <c r="K27" s="26" t="n"/>
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="J28" s="11">
-        <f>$F$32&amp;" × "&amp;$F$34</f>
+        <f>$F$32&amp;" x "&amp;$F$34</f>
         <v/>
       </c>
       <c r="K28" s="26" t="n"/>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="J30" s="11">
-        <f>$B$8&amp;" / "&amp;$F$8&amp;"  (sugerido "&amp;$F$38&amp;" / "&amp;$F$39&amp;")")</f>
+        <f>$B$8&amp;" / "&amp;$F$8&amp;" (sugerido "&amp;$F$38&amp;" / "&amp;$F$39&amp;")"</f>
         <v/>
       </c>
       <c r="K30" s="26" t="n"/>
@@ -1806,9 +1806,10 @@
           <t>Mismo Organization</t>
         </is>
       </c>
-      <c r="F37" s="11">
-        <f>OBLIGATORIO si ambos son private Dedicated</f>
-        <v/>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>OBLIGATORIO si ambos son private Dedicated</t>
+        </is>
       </c>
       <c r="G37" s="14" t="n"/>
     </row>
@@ -1843,7 +1844,7 @@
         </is>
       </c>
       <c r="F40" s="30">
-        <f>TRIM(SUBSTITUTE(SUBSTITUTE(IF(OR($F$16="SI",$F$19="SI"),"Jio: no Private Link · ","")&amp;IF(OR($B$8&lt;$F$38,$F$8&lt;$F$39),"CKU por debajo de la guía · ","")&amp;IF(OR(AND($B$7="Multi-zone",$B$8&lt;2),AND($F$7="Multi-zone",$F$8&lt;2)),"Multi-zone exige 2 CKU · ","")&amp;IF($F$21,"Cross-cloud private Cluster Linking · ","Intra-cloud private · ")&amp;IF(OR($F$15="SI",$F$18="SI"),"Premium region $5.00/h · ","")&amp;IF($F$22=2,"Bidirectional = 2 links · ","")&amp;IF(OR($F$35&lt;&gt;"OK",$F$36&lt;&gt;"OK"),"Region no coincide con cloud","")," ·  "," · "), " ·", ""))</f>
+        <f>IF(OR($F$16="SI",$F$19="SI"),"Jio: no Private Link. ","")&amp;IF(OR($B$8&lt;$F$38,$F$8&lt;$F$39),"CKU por debajo de la guia. ","")&amp;IF(OR(AND($B$7="Multi-zone",$B$8&lt;2),AND($F$7="Multi-zone",$F$8&lt;2)),"Multi-zone exige 2 CKU. ","")&amp;IF($F$21,"Cross-cloud private Cluster Linking. ","Intra-cloud private. ")&amp;IF(OR($F$15="SI",$F$18="SI"),"Premium region $5.00/h. ","")&amp;IF($F$22=2,"Bidirectional = 2 links. ","")&amp;IF(OR($F$35&lt;&gt;"OK",$F$36&lt;&gt;"OK"),"Region no coincide con cloud.","")</f>
         <v/>
       </c>
       <c r="G40" s="14" t="n"/>
@@ -2208,7 +2209,7 @@
     <row r="21">
       <c r="A21" s="33" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>REPL_FACTOR</t>
         </is>
       </c>
       <c r="B21" s="36" t="n">
@@ -2216,7 +2217,7 @@
       </c>
       <c r="C21" s="35" t="inlineStr">
         <is>
-          <t>Replication factor Dedicated. Storage ≈ 3×</t>
+          <t>Replication factor Dedicated. Storage ≈ 3x</t>
         </is>
       </c>
     </row>
